--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132901113</v>
+        <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>80346</v>
+        <v>96450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +1017,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6441</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>353896</v>
+        <v>353760</v>
       </c>
       <c r="R5" t="n">
-        <v>6514939</v>
+        <v>6514824</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1096,62 +1101,57 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901113</t>
+          <t>https://artportalen.se/Sighting/136673417</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132901110</v>
+        <v>132901113</v>
       </c>
       <c r="B6" t="n">
-        <v>8374</v>
+        <v>80346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106540</v>
+        <v>6441</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>353891</v>
+        <v>353896</v>
       </c>
       <c r="R6" t="n">
-        <v>6514932</v>
+        <v>6514939</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,38 +1209,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901110</t>
+          <t>https://artportalen.se/Sighting/132901113</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132901102</v>
+        <v>132901110</v>
       </c>
       <c r="B7" t="n">
-        <v>8449</v>
+        <v>8374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>106540</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>353742</v>
+        <v>353891</v>
       </c>
       <c r="R7" t="n">
-        <v>6514925</v>
+        <v>6514932</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,16 +1316,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901102</t>
+          <t>https://artportalen.se/Sighting/132901110</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132901101</v>
+        <v>132901102</v>
       </c>
       <c r="B8" t="n">
-        <v>101403</v>
+        <v>8449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>353720</v>
+        <v>353742</v>
       </c>
       <c r="R8" t="n">
-        <v>6514864</v>
+        <v>6514925</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,13 +1423,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901101</t>
+          <t>https://artportalen.se/Sighting/132901102</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132901103</v>
+        <v>132901101</v>
       </c>
       <c r="B9" t="n">
         <v>101403</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>353808</v>
+        <v>353720</v>
       </c>
       <c r="R9" t="n">
-        <v>6514962</v>
+        <v>6514864</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1520,13 +1525,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901103</t>
+          <t>https://artportalen.se/Sighting/132901101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132901105</v>
+        <v>132901103</v>
       </c>
       <c r="B10" t="n">
         <v>101403</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>353851</v>
+        <v>353808</v>
       </c>
       <c r="R10" t="n">
-        <v>6514937</v>
+        <v>6514962</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,13 +1627,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901105</t>
+          <t>https://artportalen.se/Sighting/132901103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132901107</v>
+        <v>132901105</v>
       </c>
       <c r="B11" t="n">
         <v>101403</v>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>353860</v>
+        <v>353851</v>
       </c>
       <c r="R11" t="n">
-        <v>6514907</v>
+        <v>6514937</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,13 +1729,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901107</t>
+          <t>https://artportalen.se/Sighting/132901105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132901109</v>
+        <v>132901107</v>
       </c>
       <c r="B12" t="n">
         <v>101403</v>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>353885</v>
+        <v>353860</v>
       </c>
       <c r="R12" t="n">
-        <v>6514915</v>
+        <v>6514907</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,13 +1831,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901109</t>
+          <t>https://artportalen.se/Sighting/132901107</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132901132</v>
+        <v>132901109</v>
       </c>
       <c r="B13" t="n">
         <v>101403</v>
@@ -1867,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>353794</v>
+        <v>353885</v>
       </c>
       <c r="R13" t="n">
-        <v>6515030</v>
+        <v>6514915</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1928,16 +1933,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901132</t>
+          <t>https://artportalen.se/Sighting/132901109</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132901112</v>
+        <v>132901132</v>
       </c>
       <c r="B14" t="n">
-        <v>80403</v>
+        <v>101403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003719</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>353895</v>
+        <v>353794</v>
       </c>
       <c r="R14" t="n">
-        <v>6514940</v>
+        <v>6515030</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2029,6 +2034,108 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901132</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132901112</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>353895</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6514940</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132901112</t>
         </is>
@@ -2049,6 +2156,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96656</v>
+        <v>96662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96461</v>
+        <v>96467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96662</v>
+        <v>96664</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96469</v>
+        <v>96470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96665</v>
+        <v>96671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96470</v>
+        <v>96476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96671</v>
+        <v>96675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96476</v>
+        <v>96480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96480</v>
+        <v>96482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96482</v>
+        <v>96484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>136592730</v>
       </c>
       <c r="B4" t="n">
-        <v>96679</v>
+        <v>96692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96484</v>
+        <v>96497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96497</v>
+        <v>96499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136673417</v>
       </c>
       <c r="B5" t="n">
-        <v>96499</v>
+        <v>96502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132901133</v>
+        <v>137408994</v>
       </c>
       <c r="B2" t="n">
-        <v>96512</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353785</v>
+        <v>353798</v>
       </c>
       <c r="R2" t="n">
-        <v>6515022</v>
+        <v>6515043</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,22 +770,22 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901133</t>
+          <t>https://artportalen.se/Sighting/137408994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132901108</v>
+        <v>132901133</v>
       </c>
       <c r="B3" t="n">
-        <v>96501</v>
+        <v>96512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353887</v>
+        <v>353785</v>
       </c>
       <c r="R3" t="n">
-        <v>6514917</v>
+        <v>6515022</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +864,21 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901108</t>
+          <t>https://artportalen.se/Sighting/132901133</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136592730</v>
+        <v>137408984</v>
       </c>
       <c r="B4" t="n">
-        <v>96692</v>
+        <v>96732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353886</v>
+        <v>353862</v>
       </c>
       <c r="R4" t="n">
-        <v>6514924</v>
+        <v>6515018</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,9 +978,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1000,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136592730</t>
+          <t>https://artportalen.se/Sighting/137408984</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136673417</v>
+        <v>137408976</v>
       </c>
       <c r="B5" t="n">
-        <v>96502</v>
+        <v>96736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,41 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>353760</v>
+        <v>353886</v>
       </c>
       <c r="R5" t="n">
-        <v>6514824</v>
+        <v>6514861</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,9 +1095,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1107,16 +1127,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673417</t>
+          <t>https://artportalen.se/Sighting/137408976</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132901113</v>
+        <v>132901108</v>
       </c>
       <c r="B6" t="n">
-        <v>80346</v>
+        <v>96501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6441</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>353896</v>
+        <v>353887</v>
       </c>
       <c r="R6" t="n">
-        <v>6514939</v>
+        <v>6514917</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,59 +1229,58 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901113</t>
+          <t>https://artportalen.se/Sighting/132901108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132901110</v>
+        <v>136592730</v>
       </c>
       <c r="B7" t="n">
-        <v>8374</v>
+        <v>96692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106540</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>353891</v>
+        <v>353886</v>
       </c>
       <c r="R7" t="n">
-        <v>6514932</v>
+        <v>6514924</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,6 +1318,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1310,22 +1330,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901110</t>
+          <t>https://artportalen.se/Sighting/136592730</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132901102</v>
+        <v>137408974</v>
       </c>
       <c r="B8" t="n">
-        <v>8449</v>
+        <v>96721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>353742</v>
+        <v>353887</v>
       </c>
       <c r="R8" t="n">
-        <v>6514925</v>
+        <v>6514858</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,12 +1407,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,22 +1432,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901102</t>
+          <t>https://artportalen.se/Sighting/137408974</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132901101</v>
+        <v>137408982</v>
       </c>
       <c r="B9" t="n">
-        <v>101403</v>
+        <v>96721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>353720</v>
+        <v>353881</v>
       </c>
       <c r="R9" t="n">
-        <v>6514864</v>
+        <v>6514962</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1494,12 +1509,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1534,22 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901101</t>
+          <t>https://artportalen.se/Sighting/137408982</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132901103</v>
+        <v>136673417</v>
       </c>
       <c r="B10" t="n">
-        <v>101403</v>
+        <v>96502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,37 +1557,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>353808</v>
+        <v>353760</v>
       </c>
       <c r="R10" t="n">
-        <v>6514962</v>
+        <v>6514824</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,12 +1615,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,6 +1629,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,22 +1641,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901103</t>
+          <t>https://artportalen.se/Sighting/136673417</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132901105</v>
+        <v>137408980</v>
       </c>
       <c r="B11" t="n">
-        <v>101403</v>
+        <v>89319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>4377</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>353851</v>
+        <v>353889</v>
       </c>
       <c r="R11" t="n">
-        <v>6514937</v>
+        <v>6514942</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1698,12 +1718,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,22 +1743,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901105</t>
+          <t>https://artportalen.se/Sighting/137408980</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132901107</v>
+        <v>137408975</v>
       </c>
       <c r="B12" t="n">
-        <v>101403</v>
+        <v>89334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,34 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>4388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Snarstigen, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>353860</v>
+        <v>353881</v>
       </c>
       <c r="R12" t="n">
-        <v>6514907</v>
+        <v>6514855</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1800,12 +1823,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,6 +1837,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1825,22 +1849,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901107</t>
+          <t>https://artportalen.se/Sighting/137408975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132901109</v>
+        <v>137408970</v>
       </c>
       <c r="B13" t="n">
-        <v>101403</v>
+        <v>93140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>353885</v>
+        <v>353867</v>
       </c>
       <c r="R13" t="n">
-        <v>6514915</v>
+        <v>6514860</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1902,12 +1926,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,22 +1951,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901109</t>
+          <t>https://artportalen.se/Sighting/137408970</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132901132</v>
+        <v>137408968</v>
       </c>
       <c r="B14" t="n">
-        <v>101403</v>
+        <v>92847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>353794</v>
+        <v>353837</v>
       </c>
       <c r="R14" t="n">
-        <v>6515030</v>
+        <v>6514907</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2004,12 +2028,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,22 +2053,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Larsson, Christine Bryngelsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132901132</t>
+          <t>https://artportalen.se/Sighting/137408968</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132901112</v>
+        <v>132901113</v>
       </c>
       <c r="B15" t="n">
-        <v>80403</v>
+        <v>80346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2076,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003719</v>
+        <v>6441</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>353895</v>
+        <v>353896</v>
       </c>
       <c r="R15" t="n">
-        <v>6514940</v>
+        <v>6514939</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2136,6 +2160,2206 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901113</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137408972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80494</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>353887</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6514876</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408972</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132901110</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8374</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>353891</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6514932</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901110</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137408973</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8383</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>353893</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6514864</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408973</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137408981</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8383</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>353880</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6514952</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408981</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132901102</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>353742</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6514925</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901102</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137408986</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>353872</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6515039</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408986</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132901101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>353720</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6514864</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132901103</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>353808</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6514962</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901103</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132901105</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>353851</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6514937</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901105</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132901107</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>353860</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6514907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901107</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132901109</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>353885</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6514915</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901109</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132901132</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>353794</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6515030</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132901132</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137408966</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>353836</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6515000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408966</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137408977</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>353887</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6514859</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408977</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137408978</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>353868</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6514873</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408978</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137408979</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>353889</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6514942</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408979</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137408983</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>353882</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6514978</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408983</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137408985</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>353868</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6515044</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408985</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137408996</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>353796</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6515022</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408996</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137408997</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>353787</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6514932</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137408997</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132901112</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Snarstigen, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>353895</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6514940</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132901112</t>
         </is>
@@ -2157,6 +4381,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408994</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>137408984</v>
       </c>
       <c r="B4" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408976</v>
       </c>
       <c r="B5" t="n">
-        <v>96736</v>
+        <v>96748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>137408974</v>
       </c>
       <c r="B8" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137408982</v>
       </c>
       <c r="B9" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137408980</v>
       </c>
       <c r="B11" t="n">
-        <v>89319</v>
+        <v>89330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>137408975</v>
       </c>
       <c r="B12" t="n">
-        <v>89334</v>
+        <v>89345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>137408970</v>
       </c>
       <c r="B13" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137408968</v>
       </c>
       <c r="B14" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>137408972</v>
       </c>
       <c r="B16" t="n">
-        <v>80494</v>
+        <v>80505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137408966</v>
       </c>
       <c r="B28" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137408977</v>
       </c>
       <c r="B29" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137408978</v>
       </c>
       <c r="B30" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137408979</v>
       </c>
       <c r="B31" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137408983</v>
       </c>
       <c r="B32" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137408985</v>
       </c>
       <c r="B33" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137408996</v>
       </c>
       <c r="B34" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137408997</v>
       </c>
       <c r="B35" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408994</v>
       </c>
       <c r="B2" t="n">
-        <v>96746</v>
+        <v>96747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>137408984</v>
       </c>
       <c r="B4" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408976</v>
       </c>
       <c r="B5" t="n">
-        <v>96748</v>
+        <v>96749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>137408974</v>
       </c>
       <c r="B8" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137408982</v>
       </c>
       <c r="B9" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137408980</v>
       </c>
       <c r="B11" t="n">
-        <v>89330</v>
+        <v>89331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>137408975</v>
       </c>
       <c r="B12" t="n">
-        <v>89345</v>
+        <v>89346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>137408970</v>
       </c>
       <c r="B13" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137408968</v>
       </c>
       <c r="B14" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>137408972</v>
       </c>
       <c r="B16" t="n">
-        <v>80505</v>
+        <v>80506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137408966</v>
       </c>
       <c r="B28" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137408977</v>
       </c>
       <c r="B29" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137408978</v>
       </c>
       <c r="B30" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137408979</v>
       </c>
       <c r="B31" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137408983</v>
       </c>
       <c r="B32" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137408985</v>
       </c>
       <c r="B33" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137408996</v>
       </c>
       <c r="B34" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137408997</v>
       </c>
       <c r="B35" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408994</v>
       </c>
       <c r="B2" t="n">
-        <v>96747</v>
+        <v>96750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>137408984</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408976</v>
       </c>
       <c r="B5" t="n">
-        <v>96749</v>
+        <v>96752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>137408974</v>
       </c>
       <c r="B8" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137408982</v>
       </c>
       <c r="B9" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137408980</v>
       </c>
       <c r="B11" t="n">
-        <v>89331</v>
+        <v>89334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>137408975</v>
       </c>
       <c r="B12" t="n">
-        <v>89346</v>
+        <v>89349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>137408970</v>
       </c>
       <c r="B13" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137408968</v>
       </c>
       <c r="B14" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>137408972</v>
       </c>
       <c r="B16" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137408966</v>
       </c>
       <c r="B28" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137408977</v>
       </c>
       <c r="B29" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137408978</v>
       </c>
       <c r="B30" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137408979</v>
       </c>
       <c r="B31" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137408983</v>
       </c>
       <c r="B32" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137408985</v>
       </c>
       <c r="B33" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137408996</v>
       </c>
       <c r="B34" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137408997</v>
       </c>
       <c r="B35" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63859-2025 artfynd.xlsx
+++ b/artfynd/A 63859-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408994</v>
       </c>
       <c r="B2" t="n">
-        <v>96750</v>
+        <v>96754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>137408984</v>
       </c>
       <c r="B4" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408976</v>
       </c>
       <c r="B5" t="n">
-        <v>96752</v>
+        <v>96756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>137408974</v>
       </c>
       <c r="B8" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137408982</v>
       </c>
       <c r="B9" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>137408980</v>
       </c>
       <c r="B11" t="n">
-        <v>89334</v>
+        <v>89338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>137408975</v>
       </c>
       <c r="B12" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>137408970</v>
       </c>
       <c r="B13" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137408968</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>137408972</v>
       </c>
       <c r="B16" t="n">
-        <v>80508</v>
+        <v>80512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>137408966</v>
       </c>
       <c r="B28" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137408977</v>
       </c>
       <c r="B29" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137408978</v>
       </c>
       <c r="B30" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>137408979</v>
       </c>
       <c r="B31" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>137408983</v>
       </c>
       <c r="B32" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137408985</v>
       </c>
       <c r="B33" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137408996</v>
       </c>
       <c r="B34" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>137408997</v>
       </c>
       <c r="B35" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
